--- a/Team-Data/2012-13/3-19-2012-13.xlsx
+++ b/Team-Data/2012-13/3-19-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>0.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
@@ -751,7 +818,7 @@
         <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI2" t="n">
         <v>11</v>
@@ -799,7 +866,7 @@
         <v>16</v>
       </c>
       <c r="AX2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY2" t="n">
         <v>6</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>0.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
         <v>12</v>
@@ -951,10 +1018,10 @@
         <v>26</v>
       </c>
       <c r="AN3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP3" t="n">
         <v>21</v>
@@ -972,10 +1039,10 @@
         <v>29</v>
       </c>
       <c r="AU3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW3" t="n">
         <v>8</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>1.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE4" t="n">
         <v>8</v>
@@ -1115,7 +1182,7 @@
         <v>9</v>
       </c>
       <c r="AH4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI4" t="n">
         <v>28</v>
@@ -1133,7 +1200,7 @@
         <v>7</v>
       </c>
       <c r="AN4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO4" t="n">
         <v>12</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-9.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>0.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="n">
         <v>12</v>
@@ -1479,7 +1546,7 @@
         <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI6" t="n">
         <v>25</v>
@@ -1518,10 +1585,10 @@
         <v>6</v>
       </c>
       <c r="AU6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW6" t="n">
         <v>19</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-3.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE7" t="n">
         <v>27</v>
@@ -1700,7 +1767,7 @@
         <v>25</v>
       </c>
       <c r="AU7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV7" t="n">
         <v>6</v>
@@ -1715,7 +1782,7 @@
         <v>29</v>
       </c>
       <c r="AZ7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>-0.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE8" t="n">
         <v>18</v>
@@ -1864,7 +1931,7 @@
         <v>6</v>
       </c>
       <c r="AO8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP8" t="n">
         <v>23</v>
@@ -1882,7 +1949,7 @@
         <v>16</v>
       </c>
       <c r="AU8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV8" t="n">
         <v>7</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F9" t="n">
         <v>22</v>
       </c>
       <c r="G9" t="n">
-        <v>0.681</v>
+        <v>0.676</v>
       </c>
       <c r="H9" t="n">
         <v>48.6</v>
@@ -1953,28 +2020,28 @@
         <v>40.8</v>
       </c>
       <c r="J9" t="n">
-        <v>85.40000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="K9" t="n">
         <v>0.478</v>
       </c>
       <c r="L9" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M9" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0.342</v>
+        <v>0.344</v>
       </c>
       <c r="O9" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="P9" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.695</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="R9" t="n">
         <v>13.4</v>
@@ -1983,7 +2050,7 @@
         <v>31.8</v>
       </c>
       <c r="T9" t="n">
-        <v>45.2</v>
+        <v>45.1</v>
       </c>
       <c r="U9" t="n">
         <v>24.4</v>
@@ -2004,25 +2071,25 @@
         <v>20.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>106.1</v>
+        <v>106</v>
       </c>
       <c r="AC9" t="n">
         <v>4.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE9" t="n">
         <v>4</v>
       </c>
       <c r="AF9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH9" t="n">
         <v>5</v>
@@ -2073,7 +2140,7 @@
         <v>2</v>
       </c>
       <c r="AX9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY9" t="n">
         <v>28</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2265,7 @@
         <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF10" t="n">
         <v>27</v>
@@ -2216,7 +2283,7 @@
         <v>20</v>
       </c>
       <c r="AK10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
         <v>23</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE12" t="n">
         <v>12</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E13" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F13" t="n">
         <v>26</v>
       </c>
       <c r="G13" t="n">
-        <v>0.618</v>
+        <v>0.612</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
@@ -2681,10 +2748,10 @@
         <v>35.1</v>
       </c>
       <c r="J13" t="n">
-        <v>81</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.433</v>
+        <v>0.434</v>
       </c>
       <c r="L13" t="n">
         <v>7.1</v>
@@ -2693,34 +2760,34 @@
         <v>19.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0.357</v>
+        <v>0.358</v>
       </c>
       <c r="O13" t="n">
         <v>17.1</v>
       </c>
       <c r="P13" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.749</v>
+        <v>0.747</v>
       </c>
       <c r="R13" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="S13" t="n">
-        <v>33.2</v>
+        <v>33</v>
       </c>
       <c r="T13" t="n">
-        <v>46.2</v>
+        <v>45.9</v>
       </c>
       <c r="U13" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V13" t="n">
         <v>15.1</v>
       </c>
       <c r="W13" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X13" t="n">
         <v>6.6</v>
@@ -2738,10 +2805,10 @@
         <v>94.40000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2762,16 +2829,16 @@
         <v>23</v>
       </c>
       <c r="AK13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL13" t="n">
         <v>15</v>
       </c>
       <c r="AM13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO13" t="n">
         <v>14</v>
@@ -2786,7 +2853,7 @@
         <v>3</v>
       </c>
       <c r="AS13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AT13" t="n">
         <v>1</v>
@@ -2801,7 +2868,7 @@
         <v>25</v>
       </c>
       <c r="AX13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY13" t="n">
         <v>21</v>
@@ -2813,7 +2880,7 @@
         <v>4</v>
       </c>
       <c r="BB13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC13" t="n">
         <v>6</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E14" t="n">
         <v>46</v>
       </c>
       <c r="F14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G14" t="n">
-        <v>0.676</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
@@ -2866,7 +2933,7 @@
         <v>80.5</v>
       </c>
       <c r="K14" t="n">
-        <v>0.476</v>
+        <v>0.477</v>
       </c>
       <c r="L14" t="n">
         <v>7.5</v>
@@ -2878,13 +2945,13 @@
         <v>0.356</v>
       </c>
       <c r="O14" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P14" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.706</v>
+        <v>0.705</v>
       </c>
       <c r="R14" t="n">
         <v>11.4</v>
@@ -2893,19 +2960,19 @@
         <v>30.1</v>
       </c>
       <c r="T14" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="U14" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="V14" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W14" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y14" t="n">
         <v>4.2</v>
@@ -2914,25 +2981,25 @@
         <v>20.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB14" t="n">
         <v>100.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AH14" t="n">
         <v>30</v>
@@ -2947,7 +3014,7 @@
         <v>5</v>
       </c>
       <c r="AL14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM14" t="n">
         <v>8</v>
@@ -2956,7 +3023,7 @@
         <v>20</v>
       </c>
       <c r="AO14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP14" t="n">
         <v>9</v>
@@ -2968,7 +3035,7 @@
         <v>15</v>
       </c>
       <c r="AS14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT14" t="n">
         <v>19</v>
@@ -2986,7 +3053,7 @@
         <v>7</v>
       </c>
       <c r="AY14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AZ14" t="n">
         <v>23</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3202,7 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO15" t="n">
         <v>4</v>
@@ -3150,7 +3217,7 @@
         <v>14</v>
       </c>
       <c r="AS15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT15" t="n">
         <v>4</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>4.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
         <v>6</v>
@@ -3296,7 +3363,7 @@
         <v>4</v>
       </c>
       <c r="AG16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH16" t="n">
         <v>21</v>
@@ -3320,7 +3387,7 @@
         <v>24</v>
       </c>
       <c r="AO16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP16" t="n">
         <v>24</v>
@@ -3356,7 +3423,7 @@
         <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB16" t="n">
         <v>26</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>7.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3499,13 +3566,13 @@
         <v>9</v>
       </c>
       <c r="AN17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO17" t="n">
         <v>10</v>
       </c>
       <c r="AP17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ17" t="n">
         <v>14</v>
@@ -3514,7 +3581,7 @@
         <v>28</v>
       </c>
       <c r="AS17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -3573,28 +3640,28 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F18" t="n">
         <v>32</v>
       </c>
       <c r="G18" t="n">
-        <v>0.515</v>
+        <v>0.508</v>
       </c>
       <c r="H18" t="n">
         <v>48.4</v>
       </c>
       <c r="I18" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J18" t="n">
         <v>86.90000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L18" t="n">
         <v>6.9</v>
@@ -3603,19 +3670,19 @@
         <v>19.1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.36</v>
+        <v>0.359</v>
       </c>
       <c r="O18" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="P18" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q18" t="n">
         <v>0.742</v>
       </c>
       <c r="R18" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="S18" t="n">
         <v>31</v>
@@ -3624,7 +3691,7 @@
         <v>43.7</v>
       </c>
       <c r="U18" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="V18" t="n">
         <v>14.2</v>
@@ -3639,22 +3706,22 @@
         <v>4.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AA18" t="n">
         <v>19.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>99.2</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AE18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF18" t="n">
         <v>15</v>
@@ -3672,7 +3739,7 @@
         <v>1</v>
       </c>
       <c r="AK18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL18" t="n">
         <v>17</v>
@@ -3681,13 +3748,13 @@
         <v>18</v>
       </c>
       <c r="AN18" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AO18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ18" t="n">
         <v>20</v>
@@ -3702,7 +3769,7 @@
         <v>5</v>
       </c>
       <c r="AU18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV18" t="n">
         <v>8</v>
@@ -3720,7 +3787,7 @@
         <v>9</v>
       </c>
       <c r="BA18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB18" t="n">
         <v>11</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -3833,10 +3900,10 @@
         <v>-3.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF19" t="n">
         <v>22</v>
@@ -3854,7 +3921,7 @@
         <v>19</v>
       </c>
       <c r="AK19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL19" t="n">
         <v>28</v>
@@ -3899,13 +3966,13 @@
         <v>24</v>
       </c>
       <c r="AZ19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA19" t="n">
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC19" t="n">
         <v>22</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-3.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE20" t="n">
         <v>27</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>2.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE21" t="n">
         <v>8</v>
@@ -4218,7 +4285,7 @@
         <v>18</v>
       </c>
       <c r="AK21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL21" t="n">
         <v>2</v>
@@ -4227,7 +4294,7 @@
         <v>2</v>
       </c>
       <c r="AN21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO21" t="n">
         <v>19</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E22" t="n">
         <v>50</v>
       </c>
       <c r="F22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G22" t="n">
-        <v>0.735</v>
+        <v>0.746</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4319,25 +4386,25 @@
         <v>38.3</v>
       </c>
       <c r="J22" t="n">
-        <v>79.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="K22" t="n">
-        <v>0.483</v>
+        <v>0.484</v>
       </c>
       <c r="L22" t="n">
         <v>7.5</v>
       </c>
       <c r="M22" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0.383</v>
+        <v>0.387</v>
       </c>
       <c r="O22" t="n">
         <v>22.7</v>
       </c>
       <c r="P22" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="Q22" t="n">
         <v>0.829</v>
@@ -4349,7 +4416,7 @@
         <v>33</v>
       </c>
       <c r="T22" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
       <c r="U22" t="n">
         <v>21.8</v>
@@ -4367,7 +4434,7 @@
         <v>4</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA22" t="n">
         <v>21.1</v>
@@ -4376,10 +4443,10 @@
         <v>106.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -4391,7 +4458,7 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI22" t="n">
         <v>7</v>
@@ -4403,13 +4470,13 @@
         <v>3</v>
       </c>
       <c r="AL22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -4424,7 +4491,7 @@
         <v>25</v>
       </c>
       <c r="AS22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
         <v>8</v>
@@ -4448,7 +4515,7 @@
         <v>18</v>
       </c>
       <c r="BA22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -4483,46 +4550,46 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E23" t="n">
         <v>18</v>
       </c>
       <c r="F23" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G23" t="n">
-        <v>0.265</v>
+        <v>0.269</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.7</v>
+        <v>37.9</v>
       </c>
       <c r="J23" t="n">
         <v>83.7</v>
       </c>
       <c r="K23" t="n">
-        <v>0.451</v>
+        <v>0.453</v>
       </c>
       <c r="L23" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M23" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0.33</v>
+        <v>0.331</v>
       </c>
       <c r="O23" t="n">
         <v>12.4</v>
       </c>
       <c r="P23" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.769</v>
+        <v>0.771</v>
       </c>
       <c r="R23" t="n">
         <v>10.5</v>
@@ -4534,7 +4601,7 @@
         <v>42.2</v>
       </c>
       <c r="U23" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="V23" t="n">
         <v>14.6</v>
@@ -4552,16 +4619,16 @@
         <v>19.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.3</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6.6</v>
+        <v>-6.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4573,13 +4640,13 @@
         <v>29</v>
       </c>
       <c r="AH23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI23" t="n">
         <v>9</v>
       </c>
       <c r="AJ23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK23" t="n">
         <v>12</v>
@@ -4600,7 +4667,7 @@
         <v>30</v>
       </c>
       <c r="AQ23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR23" t="n">
         <v>24</v>
@@ -4612,19 +4679,19 @@
         <v>15</v>
       </c>
       <c r="AU23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW23" t="n">
         <v>30</v>
       </c>
       <c r="AX23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AY23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ23" t="n">
         <v>11</v>
@@ -4633,7 +4700,7 @@
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BC23" t="n">
         <v>29</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE24" t="n">
         <v>20</v>
@@ -4761,7 +4828,7 @@
         <v>13</v>
       </c>
       <c r="AJ24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK24" t="n">
         <v>20</v>
@@ -4773,7 +4840,7 @@
         <v>24</v>
       </c>
       <c r="AN24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -4925,10 +4992,10 @@
         <v>-5.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF25" t="n">
         <v>25</v>
@@ -4937,7 +5004,7 @@
         <v>25</v>
       </c>
       <c r="AH25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI25" t="n">
         <v>15</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E26" t="n">
         <v>31</v>
       </c>
       <c r="F26" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G26" t="n">
-        <v>0.463</v>
+        <v>0.47</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
@@ -5053,19 +5120,19 @@
         <v>0.449</v>
       </c>
       <c r="L26" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0.351</v>
+        <v>0.349</v>
       </c>
       <c r="O26" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="P26" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="Q26" t="n">
         <v>0.781</v>
@@ -5074,7 +5141,7 @@
         <v>11.1</v>
       </c>
       <c r="S26" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="T26" t="n">
         <v>41.6</v>
@@ -5092,34 +5159,34 @@
         <v>4.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AB26" t="n">
         <v>98.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AE26" t="n">
         <v>19</v>
       </c>
       <c r="AF26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG26" t="n">
         <v>19</v>
       </c>
       <c r="AH26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI26" t="n">
         <v>17</v>
@@ -5131,7 +5198,7 @@
         <v>14</v>
       </c>
       <c r="AL26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM26" t="n">
         <v>4</v>
@@ -5140,7 +5207,7 @@
         <v>22</v>
       </c>
       <c r="AO26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP26" t="n">
         <v>22</v>
@@ -5158,22 +5225,22 @@
         <v>18</v>
       </c>
       <c r="AU26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW26" t="n">
         <v>26</v>
       </c>
       <c r="AX26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AY26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ26" t="n">
         <v>6</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>5</v>
       </c>
       <c r="BA26" t="n">
         <v>23</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F27" t="n">
         <v>44</v>
       </c>
       <c r="G27" t="n">
-        <v>0.353</v>
+        <v>0.343</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
@@ -5229,31 +5296,31 @@
         <v>37.3</v>
       </c>
       <c r="J27" t="n">
-        <v>83.7</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K27" t="n">
         <v>0.445</v>
       </c>
       <c r="L27" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M27" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="N27" t="n">
-        <v>0.369</v>
+        <v>0.366</v>
       </c>
       <c r="O27" t="n">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
       <c r="P27" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R27" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S27" t="n">
         <v>28.9</v>
@@ -5262,10 +5329,10 @@
         <v>40.4</v>
       </c>
       <c r="U27" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V27" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W27" t="n">
         <v>8.4</v>
@@ -5277,19 +5344,19 @@
         <v>6.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB27" t="n">
-        <v>99.7</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>-5.1</v>
+        <v>-5.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE27" t="n">
         <v>22</v>
@@ -5298,7 +5365,7 @@
         <v>24</v>
       </c>
       <c r="AG27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH27" t="n">
         <v>12</v>
@@ -5307,28 +5374,28 @@
         <v>12</v>
       </c>
       <c r="AJ27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL27" t="n">
         <v>13</v>
       </c>
       <c r="AM27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO27" t="n">
         <v>8</v>
       </c>
       <c r="AP27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR27" t="n">
         <v>13</v>
@@ -5349,13 +5416,13 @@
         <v>7</v>
       </c>
       <c r="AX27" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AY27" t="n">
         <v>27</v>
       </c>
       <c r="AZ27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA27" t="n">
         <v>14</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>8</v>
       </c>
       <c r="AD28" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5483,7 +5550,7 @@
         <v>2</v>
       </c>
       <c r="AH28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI28" t="n">
         <v>2</v>
@@ -5495,7 +5562,7 @@
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM28" t="n">
         <v>6</v>
@@ -5507,7 +5574,7 @@
         <v>15</v>
       </c>
       <c r="AP28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ28" t="n">
         <v>4</v>
@@ -5516,7 +5583,7 @@
         <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT28" t="n">
         <v>22</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-1.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
         <v>20</v>
@@ -5704,7 +5771,7 @@
         <v>27</v>
       </c>
       <c r="AU29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV29" t="n">
         <v>3</v>
@@ -5713,7 +5780,7 @@
         <v>18</v>
       </c>
       <c r="AX29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY29" t="n">
         <v>14</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-0.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE30" t="n">
         <v>16</v>
@@ -5847,7 +5914,7 @@
         <v>17</v>
       </c>
       <c r="AH30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI30" t="n">
         <v>18</v>
@@ -5865,7 +5932,7 @@
         <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO30" t="n">
         <v>5</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
@@ -6017,16 +6084,16 @@
         <v>-2.6</v>
       </c>
       <c r="AD31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE31" t="n">
         <v>22</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>23</v>
       </c>
       <c r="AF31" t="n">
         <v>23</v>
       </c>
       <c r="AG31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH31" t="n">
         <v>6</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-19-2012-13</t>
+          <t>2013-03-19</t>
         </is>
       </c>
     </row>
